--- a/data/raw/23年小德硬地技术统计-修正.xlsx
+++ b/data/raw/23年小德硬地技术统计-修正.xlsx
@@ -37,7 +37,7 @@
     <t>负责人</t>
   </si>
   <si>
-    <t>李星云</t>
+    <t>Study team</t>
   </si>
   <si>
     <t>场次信息</t>
